--- a/TEM_dcf.xlsx
+++ b/TEM_dcf.xlsx
@@ -17,12 +17,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0x"/>
-    <numFmt numFmtId="168" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -66,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -75,7 +74,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -83,7 +82,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,11 +450,11 @@
   <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,7 +522,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Source: EDGAR RevenueFromContractWithCustomer</t>
+          <t>Source: EDGAR</t>
         </is>
       </c>
     </row>
@@ -545,14 +543,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Derived: CostsAndExpenses − SG&amp;A − R&amp;D</t>
+          <t>Source / derived</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Gross Profit ($000s)</t>
         </is>
       </c>
       <c r="B8" s="2">
@@ -614,7 +612,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Source: EDGAR GeneralAndAdministrativeExpense (incl SBC)</t>
+          <t>Source: EDGAR</t>
         </is>
       </c>
     </row>
@@ -635,7 +633,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Source: EDGAR ResearchAndDevelopmentExpense</t>
+          <t>Source: EDGAR</t>
         </is>
       </c>
     </row>
@@ -656,7 +654,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Source: EDGAR OperatingIncomeLoss</t>
+          <t>Source: EDGAR</t>
         </is>
       </c>
     </row>
@@ -677,7 +675,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Source: EDGAR DepreciationDepletionAndAmortization</t>
+          <t>Source: EDGAR Cash Flow</t>
         </is>
       </c>
     </row>
@@ -698,7 +696,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Source: EDGAR AllocatedShareBasedCompensationExpense</t>
+          <t>Source: EDGAR Cash Flow</t>
         </is>
       </c>
     </row>
@@ -719,7 +717,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Source: EDGAR PaymentsToAcquirePropertyPlantAndEquipment</t>
+          <t>Source: EDGAR Cash Flow</t>
         </is>
       </c>
     </row>
@@ -740,7 +738,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Source: EDGAR CapitalizedComputerSoftwareAdditions</t>
+          <t>Source: EDGAR</t>
         </is>
       </c>
     </row>
@@ -761,7 +759,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Source: EDGAR InterestExpenseDebt</t>
+          <t>Source: EDGAR</t>
         </is>
       </c>
     </row>
@@ -782,7 +780,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Source: EDGAR InvestmentIncomeInterest</t>
+          <t>Source: EDGAR</t>
         </is>
       </c>
     </row>
@@ -803,14 +801,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Source: EDGAR NetIncomeLoss</t>
+          <t>Source: EDGAR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>A2.  BALANCE SHEET SNAPSHOT  (Source: TEM 10-K FY2025, SEC EDGAR)</t>
+          <t>A2.  BALANCE SHEET SNAPSHOT  (Source: TEM 10-K FY2025, SEC EDGAR CIK 0001717115)</t>
         </is>
       </c>
     </row>
@@ -850,7 +848,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EDGAR CashAndCashEquivalentsAtCarryingValue</t>
+          <t>EDGAR Cash</t>
         </is>
       </c>
     </row>
@@ -868,7 +866,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TEM: none reported</t>
+          <t>EDGAR / 0 if none</t>
         </is>
       </c>
     </row>
@@ -886,7 +884,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TEM: none reported</t>
+          <t>EDGAR / 0 if none</t>
         </is>
       </c>
     </row>
@@ -924,7 +922,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>EDGAR AccountsReceivableNetCurrent</t>
+          <t>EDGAR AR</t>
         </is>
       </c>
     </row>
@@ -942,7 +940,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>EDGAR Goodwill (inc. Ambry Genetics acq. FY2025)</t>
+          <t>EDGAR Goodwill</t>
         </is>
       </c>
     </row>
@@ -960,14 +958,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>EDGAR IntangibleAssetsNetExcludingGoodwill</t>
+          <t>EDGAR Intangibles</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Total Debt (Convertible Notes)</t>
+          <t>Total Debt (Gross Principal)</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -978,23 +976,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>EDGAR ConvertibleDebtNoncurrent</t>
+          <t>EDGAR Debt</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Debt Used in Bridge</t>
-        </is>
-      </c>
-      <c r="B32">
+          <t>Debt Used in Bridge (Conv. Notes)</t>
+        </is>
+      </c>
+      <c r="B32" s="2">
         <f>B31</f>
         <v/>
       </c>
-      <c r="C32">
-        <f>C31</f>
-        <v/>
+      <c r="C32" s="2" t="n">
+        <v>208672</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1016,7 +1013,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>EDGAR WeightedAverageDilutedShares × 1000</t>
+          <t>EDGAR diluted shares</t>
         </is>
       </c>
     </row>
@@ -1026,24 +1023,23 @@
           <t>Shares Used in Bridge</t>
         </is>
       </c>
-      <c r="B34">
+      <c r="B34" s="2">
         <f>B33</f>
         <v/>
       </c>
-      <c r="C34">
-        <f>C33</f>
-        <v/>
+      <c r="C34" s="2" t="n">
+        <v>174264000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Formula: use FY2025 diluted count</t>
+          <t>FY2025 diluted weighted-average × 1000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Federal NOL (DTA proxy, $K)</t>
+          <t>Federal NOL Carryforward ($K)</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1146,11 +1142,7 @@
       <c r="D42" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Continued AI/oncology expansion</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1167,11 +1159,7 @@
       <c r="D43" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Scale + payer contract wins</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1190,14 +1178,14 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TAM penetration; platform maturation</t>
+          <t>TAM penetration</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FY2031–2035 Revenue CAGR</t>
+          <t>FY2031–2035 Revenue Growth Rate</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
@@ -1209,16 +1197,12 @@
       <c r="D45" s="4" t="n">
         <v>0.08</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Maturing growth; international entry</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FY2036–2040 Revenue CAGR</t>
+          <t>FY2036–2040 Revenue Growth Rate</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
@@ -1230,16 +1214,12 @@
       <c r="D46" s="4" t="n">
         <v>0.06</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Large base; moderate compounding</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FY2041–2045 Revenue CAGR</t>
+          <t>FY2041–2045 Revenue Growth Rate</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
@@ -1251,11 +1231,7 @@
       <c r="D47" s="4" t="n">
         <v>0.04</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Terminal approach; long-run normalization</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1349,11 +1325,7 @@
       <c r="D55" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Platform mix shift; sequencing cost decline</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1370,11 +1342,7 @@
       <c r="D56" s="6" t="n">
         <v>0.52</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Software-driven revenue grows faster</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1391,11 +1359,7 @@
       <c r="D57" s="6" t="n">
         <v>0.54</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Scale economics</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1412,11 +1376,7 @@
       <c r="D58" s="6" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Mature platform mix</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1433,11 +1393,7 @@
       <c r="D59" s="6" t="n">
         <v>0.58</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Long-run target; health-AI SaaS peers 65–75%</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1454,11 +1410,7 @@
       <c r="D60" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Terminal gross margin</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1477,7 +1429,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FY2025=57.5% (incl SBC); heavy sales investment</t>
+          <t>FY2025=57.5% incl SBC; heavy sales investment</t>
         </is>
       </c>
     </row>
@@ -1496,11 +1448,7 @@
       <c r="D62" s="6" t="n">
         <v>0.52</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Operating leverage begins</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1568,11 +1516,7 @@
       <c r="D66" s="6" t="n">
         <v>0.34</v>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Maturing cost structure</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1589,11 +1533,7 @@
       <c r="D67" s="6" t="n">
         <v>0.28</v>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Terminal SG&amp;A</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1633,7 +1573,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Elevated post-Ambry intangible amort (~$355M)</t>
+          <t>Elevated post-Ambry intangible amort</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1594,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Asset-light; FY2025 CapEx+CapSW=2.1% rev</t>
+          <t>Asset-light; FY2025=2.1% rev</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1613,7 @@
       <c r="D71" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>FY2025=9.8%; normalizing from IPO spike</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1696,7 +1632,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AR-heavy model; genomics payer lag</t>
+          <t>AR-heavy; genomics payer lag</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1653,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>$727M DTA / large NOL; ~0% cash tax 8–10 yrs</t>
+          <t>$727M DTA / large NOL</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1729,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>10-yr US Treasury; as of model date May 2026</t>
+          <t>10-yr US Treasury May 2026</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1750,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Damodaran US ERP estimate</t>
+          <t>Damodaran US ERP</t>
         </is>
       </c>
     </row>
@@ -1854,11 +1790,7 @@
       <c r="D82" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Mid-cap premium; TEM mkt cap ~$8–12B range</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1899,11 +1831,7 @@
       <c r="D84" s="6" t="n">
         <v>0.065</v>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Convertible notes; blended coupon est.</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1920,11 +1848,7 @@
       <c r="D85" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Post-debt capital structure</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2046,7 +1970,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Health-tech/AI software comps 15–30×</t>
+          <t>Comp range</t>
         </is>
       </c>
     </row>
@@ -2065,11 +1989,7 @@
       <c r="D94" s="4" t="n">
         <v>0.18</v>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Long-run Adj. EBITDA margin target</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -2124,11 +2044,7 @@
         <f>B79*B85</f>
         <v/>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Falls automatically if rates cut</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2149,11 +2065,7 @@
         <f>B81*B80*B85</f>
         <v/>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Market-wide; not controllable</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2167,18 +2079,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Currently 1.70</t>
+          <t>Levered beta</t>
         </is>
       </c>
       <c r="D101" s="3">
         <f>B81*B80*B85</f>
         <v/>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Cut to 1.0–1.2 once FCF-positive, revenue diversified</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2192,18 +2100,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Currently 2%</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="D102" s="3">
         <f>B82*B85</f>
         <v/>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Drops to 0% once mkt cap &gt;$5B consistently</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2217,18 +2121,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Rf + Beta×ERP + Size</t>
+          <t>Rf+Beta×ERP+Size</t>
         </is>
       </c>
       <c r="D103" s="3">
         <f>B83*B85</f>
         <v/>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Currently ~16%; driven by Beta and Size</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2242,23 +2142,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Conv. notes ~5.5%</t>
+          <t>Pre-tax × (1-t)</t>
         </is>
       </c>
       <c r="D104" s="3">
         <f>B84*(1-D74)*B86</f>
         <v/>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Minor — 15% weight, convertible structure</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>WACC  (Ke×We + Kd×(1−t)×Wd)</t>
+          <t>WACC</t>
         </is>
       </c>
       <c r="B105">
@@ -2270,11 +2166,7 @@
           <t>Formula result</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>PRIMARY: Beta 1.70→1.0 saves ~4pp; Size saves ~1.7pp</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -2330,7 +2222,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pre-profit; heavy SBC; concentrated revenue</t>
+          <t>Pre-profit baseline</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2239,7 @@
         <v>0.015</v>
       </c>
       <c r="D110" s="3">
-        <f>(B79+1.30*B80+0.015)*B85+B84*(1-D74)*B86</f>
+        <f>(B79+1.3*B80+0.015)*B85+B84*(1-D74)*B86</f>
         <v/>
       </c>
       <c r="E110" t="inlineStr">
@@ -2369,12 +2261,12 @@
         <v>0.005</v>
       </c>
       <c r="D111" s="3">
-        <f>(B79+1.00*B80+0.005)*B85+B84*(1-D74)*B86</f>
+        <f>(B79+1.0*B80+0.005)*B85+B84*(1-D74)*B86</f>
         <v/>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ARR visible; genomics recurring revenue scaling</t>
+          <t>ARR visible; genomics recurring revenue</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2283,12 @@
         <v>0</v>
       </c>
       <c r="D112" s="3">
-        <f>(B79+0.80*B80+0.000)*B85+B84*(1-D74)*B86</f>
+        <f>(B79+0.8*B80+0.0)*B85+B84*(1-D74)*B86</f>
         <v/>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Debt-free, profitable 3+ yrs, category leader</t>
+          <t>Debt-free, profitable 3+ yrs</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2305,12 @@
         <v>0</v>
       </c>
       <c r="D113" s="3">
-        <f>(B79+0.60*B80+0.000)*B85+B84*(1-D74)*B86</f>
+        <f>(B79+0.6*B80+0.0)*B85+B84*(1-D74)*B86</f>
         <v/>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Tempus moat/brand = health-AI infrastructure</t>
+          <t>Tempus moat = health-AI infrastructure</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4835,7 @@
           <t xml:space="preserve">   Exit EV/EBITDA Multiple (Active Scenario)</t>
         </is>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="11">
         <f>CHOOSE(Assumptions!B50,Assumptions!B93,Assumptions!C93,Assumptions!D93)</f>
         <v/>
       </c>
@@ -5009,11 +4901,6 @@
         <f>MAX(0,Assumptions!C32-Assumptions!C27)</f>
         <v/>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>If liquidity &gt; debt, TEM is net cash — add back in equity bridge</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5054,7 +4941,7 @@
           <t>IMPLIED SHARE PRICE ($)</t>
         </is>
       </c>
-      <c r="B55" s="14">
+      <c r="B55" s="13">
         <f>IF(B54&gt;0,(B53*1000)/B54,0)</f>
         <v/>
       </c>
@@ -5325,15 +5212,15 @@
           <t>Implied Share Price ($)</t>
         </is>
       </c>
-      <c r="B71" s="14">
+      <c r="B71" s="13">
         <f>B167</f>
         <v/>
       </c>
-      <c r="C71" s="14">
+      <c r="C71" s="13">
         <f>C167</f>
         <v/>
       </c>
-      <c r="D71" s="14">
+      <c r="D71" s="13">
         <f>D167</f>
         <v/>
       </c>
@@ -5341,7 +5228,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>H.  SENSITIVITY: Implied Share Price ($)  —  WACC vs Terminal Growth Rate  (Base Case revenue/margins)</t>
+          <t>H.  SENSITIVITY: Implied Share Price ($)  —  WACC vs Terminal Growth Rate  (Base Case)</t>
         </is>
       </c>
     </row>
@@ -5388,27 +5275,27 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="B76" s="14">
+      <c r="B76" s="13">
         <f>IF(0.1&gt;0.02,(B122/(1+0.1)^0.5+B123/(1+0.1)^1.5+B124/(1+0.1)^2.5+B125/(1+0.1)^3.5+B126/(1+0.1)^4.5+B127/(1+0.1)^5.5+B128/(1+0.1)^6.5+B129/(1+0.1)^7.5+B130/(1+0.1)^8.5+B131/(1+0.1)^9.5+B132/(1+0.1)^10.5+B133/(1+0.1)^11.5+B134/(1+0.1)^12.5+B135/(1+0.1)^13.5+B136/(1+0.1)^14.5+B137/(1+0.1)^15.5+B138/(1+0.1)^16.5+B139/(1+0.1)^17.5+B140/(1+0.1)^18.5+B141/(1+0.1)^19.5+B141*(1+0.02)/(0.1-0.02)/(1+0.1)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="C76" s="14">
+      <c r="C76" s="13">
         <f>IF(0.1&gt;0.025,(B122/(1+0.1)^0.5+B123/(1+0.1)^1.5+B124/(1+0.1)^2.5+B125/(1+0.1)^3.5+B126/(1+0.1)^4.5+B127/(1+0.1)^5.5+B128/(1+0.1)^6.5+B129/(1+0.1)^7.5+B130/(1+0.1)^8.5+B131/(1+0.1)^9.5+B132/(1+0.1)^10.5+B133/(1+0.1)^11.5+B134/(1+0.1)^12.5+B135/(1+0.1)^13.5+B136/(1+0.1)^14.5+B137/(1+0.1)^15.5+B138/(1+0.1)^16.5+B139/(1+0.1)^17.5+B140/(1+0.1)^18.5+B141/(1+0.1)^19.5+B141*(1+0.025)/(0.1-0.025)/(1+0.1)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="D76" s="14">
+      <c r="D76" s="13">
         <f>IF(0.1&gt;0.03,(B122/(1+0.1)^0.5+B123/(1+0.1)^1.5+B124/(1+0.1)^2.5+B125/(1+0.1)^3.5+B126/(1+0.1)^4.5+B127/(1+0.1)^5.5+B128/(1+0.1)^6.5+B129/(1+0.1)^7.5+B130/(1+0.1)^8.5+B131/(1+0.1)^9.5+B132/(1+0.1)^10.5+B133/(1+0.1)^11.5+B134/(1+0.1)^12.5+B135/(1+0.1)^13.5+B136/(1+0.1)^14.5+B137/(1+0.1)^15.5+B138/(1+0.1)^16.5+B139/(1+0.1)^17.5+B140/(1+0.1)^18.5+B141/(1+0.1)^19.5+B141*(1+0.03)/(0.1-0.03)/(1+0.1)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="E76" s="14">
+      <c r="E76" s="13">
         <f>IF(0.1&gt;0.035,(B122/(1+0.1)^0.5+B123/(1+0.1)^1.5+B124/(1+0.1)^2.5+B125/(1+0.1)^3.5+B126/(1+0.1)^4.5+B127/(1+0.1)^5.5+B128/(1+0.1)^6.5+B129/(1+0.1)^7.5+B130/(1+0.1)^8.5+B131/(1+0.1)^9.5+B132/(1+0.1)^10.5+B133/(1+0.1)^11.5+B134/(1+0.1)^12.5+B135/(1+0.1)^13.5+B136/(1+0.1)^14.5+B137/(1+0.1)^15.5+B138/(1+0.1)^16.5+B139/(1+0.1)^17.5+B140/(1+0.1)^18.5+B141/(1+0.1)^19.5+B141*(1+0.035)/(0.1-0.035)/(1+0.1)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="F76" s="14">
+      <c r="F76" s="13">
         <f>IF(0.1&gt;0.04,(B122/(1+0.1)^0.5+B123/(1+0.1)^1.5+B124/(1+0.1)^2.5+B125/(1+0.1)^3.5+B126/(1+0.1)^4.5+B127/(1+0.1)^5.5+B128/(1+0.1)^6.5+B129/(1+0.1)^7.5+B130/(1+0.1)^8.5+B131/(1+0.1)^9.5+B132/(1+0.1)^10.5+B133/(1+0.1)^11.5+B134/(1+0.1)^12.5+B135/(1+0.1)^13.5+B136/(1+0.1)^14.5+B137/(1+0.1)^15.5+B138/(1+0.1)^16.5+B139/(1+0.1)^17.5+B140/(1+0.1)^18.5+B141/(1+0.1)^19.5+B141*(1+0.04)/(0.1-0.04)/(1+0.1)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="G76" s="14">
+      <c r="G76" s="13">
         <f>IF(0.1&gt;0.045,(B122/(1+0.1)^0.5+B123/(1+0.1)^1.5+B124/(1+0.1)^2.5+B125/(1+0.1)^3.5+B126/(1+0.1)^4.5+B127/(1+0.1)^5.5+B128/(1+0.1)^6.5+B129/(1+0.1)^7.5+B130/(1+0.1)^8.5+B131/(1+0.1)^9.5+B132/(1+0.1)^10.5+B133/(1+0.1)^11.5+B134/(1+0.1)^12.5+B135/(1+0.1)^13.5+B136/(1+0.1)^14.5+B137/(1+0.1)^15.5+B138/(1+0.1)^16.5+B139/(1+0.1)^17.5+B140/(1+0.1)^18.5+B141/(1+0.1)^19.5+B141*(1+0.045)/(0.1-0.045)/(1+0.1)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
@@ -5419,27 +5306,27 @@
           <t>12%</t>
         </is>
       </c>
-      <c r="B77" s="14">
+      <c r="B77" s="13">
         <f>IF(0.12&gt;0.02,(B122/(1+0.12)^0.5+B123/(1+0.12)^1.5+B124/(1+0.12)^2.5+B125/(1+0.12)^3.5+B126/(1+0.12)^4.5+B127/(1+0.12)^5.5+B128/(1+0.12)^6.5+B129/(1+0.12)^7.5+B130/(1+0.12)^8.5+B131/(1+0.12)^9.5+B132/(1+0.12)^10.5+B133/(1+0.12)^11.5+B134/(1+0.12)^12.5+B135/(1+0.12)^13.5+B136/(1+0.12)^14.5+B137/(1+0.12)^15.5+B138/(1+0.12)^16.5+B139/(1+0.12)^17.5+B140/(1+0.12)^18.5+B141/(1+0.12)^19.5+B141*(1+0.02)/(0.12-0.02)/(1+0.12)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="C77" s="14">
+      <c r="C77" s="13">
         <f>IF(0.12&gt;0.025,(B122/(1+0.12)^0.5+B123/(1+0.12)^1.5+B124/(1+0.12)^2.5+B125/(1+0.12)^3.5+B126/(1+0.12)^4.5+B127/(1+0.12)^5.5+B128/(1+0.12)^6.5+B129/(1+0.12)^7.5+B130/(1+0.12)^8.5+B131/(1+0.12)^9.5+B132/(1+0.12)^10.5+B133/(1+0.12)^11.5+B134/(1+0.12)^12.5+B135/(1+0.12)^13.5+B136/(1+0.12)^14.5+B137/(1+0.12)^15.5+B138/(1+0.12)^16.5+B139/(1+0.12)^17.5+B140/(1+0.12)^18.5+B141/(1+0.12)^19.5+B141*(1+0.025)/(0.12-0.025)/(1+0.12)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="D77" s="14">
+      <c r="D77" s="13">
         <f>IF(0.12&gt;0.03,(B122/(1+0.12)^0.5+B123/(1+0.12)^1.5+B124/(1+0.12)^2.5+B125/(1+0.12)^3.5+B126/(1+0.12)^4.5+B127/(1+0.12)^5.5+B128/(1+0.12)^6.5+B129/(1+0.12)^7.5+B130/(1+0.12)^8.5+B131/(1+0.12)^9.5+B132/(1+0.12)^10.5+B133/(1+0.12)^11.5+B134/(1+0.12)^12.5+B135/(1+0.12)^13.5+B136/(1+0.12)^14.5+B137/(1+0.12)^15.5+B138/(1+0.12)^16.5+B139/(1+0.12)^17.5+B140/(1+0.12)^18.5+B141/(1+0.12)^19.5+B141*(1+0.03)/(0.12-0.03)/(1+0.12)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="E77" s="14">
+      <c r="E77" s="13">
         <f>IF(0.12&gt;0.035,(B122/(1+0.12)^0.5+B123/(1+0.12)^1.5+B124/(1+0.12)^2.5+B125/(1+0.12)^3.5+B126/(1+0.12)^4.5+B127/(1+0.12)^5.5+B128/(1+0.12)^6.5+B129/(1+0.12)^7.5+B130/(1+0.12)^8.5+B131/(1+0.12)^9.5+B132/(1+0.12)^10.5+B133/(1+0.12)^11.5+B134/(1+0.12)^12.5+B135/(1+0.12)^13.5+B136/(1+0.12)^14.5+B137/(1+0.12)^15.5+B138/(1+0.12)^16.5+B139/(1+0.12)^17.5+B140/(1+0.12)^18.5+B141/(1+0.12)^19.5+B141*(1+0.035)/(0.12-0.035)/(1+0.12)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="F77" s="14">
+      <c r="F77" s="13">
         <f>IF(0.12&gt;0.04,(B122/(1+0.12)^0.5+B123/(1+0.12)^1.5+B124/(1+0.12)^2.5+B125/(1+0.12)^3.5+B126/(1+0.12)^4.5+B127/(1+0.12)^5.5+B128/(1+0.12)^6.5+B129/(1+0.12)^7.5+B130/(1+0.12)^8.5+B131/(1+0.12)^9.5+B132/(1+0.12)^10.5+B133/(1+0.12)^11.5+B134/(1+0.12)^12.5+B135/(1+0.12)^13.5+B136/(1+0.12)^14.5+B137/(1+0.12)^15.5+B138/(1+0.12)^16.5+B139/(1+0.12)^17.5+B140/(1+0.12)^18.5+B141/(1+0.12)^19.5+B141*(1+0.04)/(0.12-0.04)/(1+0.12)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="G77" s="14">
+      <c r="G77" s="13">
         <f>IF(0.12&gt;0.045,(B122/(1+0.12)^0.5+B123/(1+0.12)^1.5+B124/(1+0.12)^2.5+B125/(1+0.12)^3.5+B126/(1+0.12)^4.5+B127/(1+0.12)^5.5+B128/(1+0.12)^6.5+B129/(1+0.12)^7.5+B130/(1+0.12)^8.5+B131/(1+0.12)^9.5+B132/(1+0.12)^10.5+B133/(1+0.12)^11.5+B134/(1+0.12)^12.5+B135/(1+0.12)^13.5+B136/(1+0.12)^14.5+B137/(1+0.12)^15.5+B138/(1+0.12)^16.5+B139/(1+0.12)^17.5+B140/(1+0.12)^18.5+B141/(1+0.12)^19.5+B141*(1+0.045)/(0.12-0.045)/(1+0.12)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
@@ -5450,27 +5337,27 @@
           <t>14%</t>
         </is>
       </c>
-      <c r="B78" s="14">
+      <c r="B78" s="13">
         <f>IF(0.14&gt;0.02,(B122/(1+0.14)^0.5+B123/(1+0.14)^1.5+B124/(1+0.14)^2.5+B125/(1+0.14)^3.5+B126/(1+0.14)^4.5+B127/(1+0.14)^5.5+B128/(1+0.14)^6.5+B129/(1+0.14)^7.5+B130/(1+0.14)^8.5+B131/(1+0.14)^9.5+B132/(1+0.14)^10.5+B133/(1+0.14)^11.5+B134/(1+0.14)^12.5+B135/(1+0.14)^13.5+B136/(1+0.14)^14.5+B137/(1+0.14)^15.5+B138/(1+0.14)^16.5+B139/(1+0.14)^17.5+B140/(1+0.14)^18.5+B141/(1+0.14)^19.5+B141*(1+0.02)/(0.14-0.02)/(1+0.14)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="C78" s="14">
+      <c r="C78" s="13">
         <f>IF(0.14&gt;0.025,(B122/(1+0.14)^0.5+B123/(1+0.14)^1.5+B124/(1+0.14)^2.5+B125/(1+0.14)^3.5+B126/(1+0.14)^4.5+B127/(1+0.14)^5.5+B128/(1+0.14)^6.5+B129/(1+0.14)^7.5+B130/(1+0.14)^8.5+B131/(1+0.14)^9.5+B132/(1+0.14)^10.5+B133/(1+0.14)^11.5+B134/(1+0.14)^12.5+B135/(1+0.14)^13.5+B136/(1+0.14)^14.5+B137/(1+0.14)^15.5+B138/(1+0.14)^16.5+B139/(1+0.14)^17.5+B140/(1+0.14)^18.5+B141/(1+0.14)^19.5+B141*(1+0.025)/(0.14-0.025)/(1+0.14)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="D78" s="14">
+      <c r="D78" s="13">
         <f>IF(0.14&gt;0.03,(B122/(1+0.14)^0.5+B123/(1+0.14)^1.5+B124/(1+0.14)^2.5+B125/(1+0.14)^3.5+B126/(1+0.14)^4.5+B127/(1+0.14)^5.5+B128/(1+0.14)^6.5+B129/(1+0.14)^7.5+B130/(1+0.14)^8.5+B131/(1+0.14)^9.5+B132/(1+0.14)^10.5+B133/(1+0.14)^11.5+B134/(1+0.14)^12.5+B135/(1+0.14)^13.5+B136/(1+0.14)^14.5+B137/(1+0.14)^15.5+B138/(1+0.14)^16.5+B139/(1+0.14)^17.5+B140/(1+0.14)^18.5+B141/(1+0.14)^19.5+B141*(1+0.03)/(0.14-0.03)/(1+0.14)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="E78" s="14">
+      <c r="E78" s="13">
         <f>IF(0.14&gt;0.035,(B122/(1+0.14)^0.5+B123/(1+0.14)^1.5+B124/(1+0.14)^2.5+B125/(1+0.14)^3.5+B126/(1+0.14)^4.5+B127/(1+0.14)^5.5+B128/(1+0.14)^6.5+B129/(1+0.14)^7.5+B130/(1+0.14)^8.5+B131/(1+0.14)^9.5+B132/(1+0.14)^10.5+B133/(1+0.14)^11.5+B134/(1+0.14)^12.5+B135/(1+0.14)^13.5+B136/(1+0.14)^14.5+B137/(1+0.14)^15.5+B138/(1+0.14)^16.5+B139/(1+0.14)^17.5+B140/(1+0.14)^18.5+B141/(1+0.14)^19.5+B141*(1+0.035)/(0.14-0.035)/(1+0.14)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="F78" s="14">
+      <c r="F78" s="13">
         <f>IF(0.14&gt;0.04,(B122/(1+0.14)^0.5+B123/(1+0.14)^1.5+B124/(1+0.14)^2.5+B125/(1+0.14)^3.5+B126/(1+0.14)^4.5+B127/(1+0.14)^5.5+B128/(1+0.14)^6.5+B129/(1+0.14)^7.5+B130/(1+0.14)^8.5+B131/(1+0.14)^9.5+B132/(1+0.14)^10.5+B133/(1+0.14)^11.5+B134/(1+0.14)^12.5+B135/(1+0.14)^13.5+B136/(1+0.14)^14.5+B137/(1+0.14)^15.5+B138/(1+0.14)^16.5+B139/(1+0.14)^17.5+B140/(1+0.14)^18.5+B141/(1+0.14)^19.5+B141*(1+0.04)/(0.14-0.04)/(1+0.14)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="G78" s="14">
+      <c r="G78" s="13">
         <f>IF(0.14&gt;0.045,(B122/(1+0.14)^0.5+B123/(1+0.14)^1.5+B124/(1+0.14)^2.5+B125/(1+0.14)^3.5+B126/(1+0.14)^4.5+B127/(1+0.14)^5.5+B128/(1+0.14)^6.5+B129/(1+0.14)^7.5+B130/(1+0.14)^8.5+B131/(1+0.14)^9.5+B132/(1+0.14)^10.5+B133/(1+0.14)^11.5+B134/(1+0.14)^12.5+B135/(1+0.14)^13.5+B136/(1+0.14)^14.5+B137/(1+0.14)^15.5+B138/(1+0.14)^16.5+B139/(1+0.14)^17.5+B140/(1+0.14)^18.5+B141/(1+0.14)^19.5+B141*(1+0.045)/(0.14-0.045)/(1+0.14)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
@@ -5481,27 +5368,27 @@
           <t>16%</t>
         </is>
       </c>
-      <c r="B79" s="14">
+      <c r="B79" s="13">
         <f>IF(0.16&gt;0.02,(B122/(1+0.16)^0.5+B123/(1+0.16)^1.5+B124/(1+0.16)^2.5+B125/(1+0.16)^3.5+B126/(1+0.16)^4.5+B127/(1+0.16)^5.5+B128/(1+0.16)^6.5+B129/(1+0.16)^7.5+B130/(1+0.16)^8.5+B131/(1+0.16)^9.5+B132/(1+0.16)^10.5+B133/(1+0.16)^11.5+B134/(1+0.16)^12.5+B135/(1+0.16)^13.5+B136/(1+0.16)^14.5+B137/(1+0.16)^15.5+B138/(1+0.16)^16.5+B139/(1+0.16)^17.5+B140/(1+0.16)^18.5+B141/(1+0.16)^19.5+B141*(1+0.02)/(0.16-0.02)/(1+0.16)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="C79" s="14">
+      <c r="C79" s="13">
         <f>IF(0.16&gt;0.025,(B122/(1+0.16)^0.5+B123/(1+0.16)^1.5+B124/(1+0.16)^2.5+B125/(1+0.16)^3.5+B126/(1+0.16)^4.5+B127/(1+0.16)^5.5+B128/(1+0.16)^6.5+B129/(1+0.16)^7.5+B130/(1+0.16)^8.5+B131/(1+0.16)^9.5+B132/(1+0.16)^10.5+B133/(1+0.16)^11.5+B134/(1+0.16)^12.5+B135/(1+0.16)^13.5+B136/(1+0.16)^14.5+B137/(1+0.16)^15.5+B138/(1+0.16)^16.5+B139/(1+0.16)^17.5+B140/(1+0.16)^18.5+B141/(1+0.16)^19.5+B141*(1+0.025)/(0.16-0.025)/(1+0.16)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="D79" s="14">
+      <c r="D79" s="13">
         <f>IF(0.16&gt;0.03,(B122/(1+0.16)^0.5+B123/(1+0.16)^1.5+B124/(1+0.16)^2.5+B125/(1+0.16)^3.5+B126/(1+0.16)^4.5+B127/(1+0.16)^5.5+B128/(1+0.16)^6.5+B129/(1+0.16)^7.5+B130/(1+0.16)^8.5+B131/(1+0.16)^9.5+B132/(1+0.16)^10.5+B133/(1+0.16)^11.5+B134/(1+0.16)^12.5+B135/(1+0.16)^13.5+B136/(1+0.16)^14.5+B137/(1+0.16)^15.5+B138/(1+0.16)^16.5+B139/(1+0.16)^17.5+B140/(1+0.16)^18.5+B141/(1+0.16)^19.5+B141*(1+0.03)/(0.16-0.03)/(1+0.16)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="E79" s="14">
+      <c r="E79" s="13">
         <f>IF(0.16&gt;0.035,(B122/(1+0.16)^0.5+B123/(1+0.16)^1.5+B124/(1+0.16)^2.5+B125/(1+0.16)^3.5+B126/(1+0.16)^4.5+B127/(1+0.16)^5.5+B128/(1+0.16)^6.5+B129/(1+0.16)^7.5+B130/(1+0.16)^8.5+B131/(1+0.16)^9.5+B132/(1+0.16)^10.5+B133/(1+0.16)^11.5+B134/(1+0.16)^12.5+B135/(1+0.16)^13.5+B136/(1+0.16)^14.5+B137/(1+0.16)^15.5+B138/(1+0.16)^16.5+B139/(1+0.16)^17.5+B140/(1+0.16)^18.5+B141/(1+0.16)^19.5+B141*(1+0.035)/(0.16-0.035)/(1+0.16)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="F79" s="14">
+      <c r="F79" s="13">
         <f>IF(0.16&gt;0.04,(B122/(1+0.16)^0.5+B123/(1+0.16)^1.5+B124/(1+0.16)^2.5+B125/(1+0.16)^3.5+B126/(1+0.16)^4.5+B127/(1+0.16)^5.5+B128/(1+0.16)^6.5+B129/(1+0.16)^7.5+B130/(1+0.16)^8.5+B131/(1+0.16)^9.5+B132/(1+0.16)^10.5+B133/(1+0.16)^11.5+B134/(1+0.16)^12.5+B135/(1+0.16)^13.5+B136/(1+0.16)^14.5+B137/(1+0.16)^15.5+B138/(1+0.16)^16.5+B139/(1+0.16)^17.5+B140/(1+0.16)^18.5+B141/(1+0.16)^19.5+B141*(1+0.04)/(0.16-0.04)/(1+0.16)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="G79" s="14">
+      <c r="G79" s="13">
         <f>IF(0.16&gt;0.045,(B122/(1+0.16)^0.5+B123/(1+0.16)^1.5+B124/(1+0.16)^2.5+B125/(1+0.16)^3.5+B126/(1+0.16)^4.5+B127/(1+0.16)^5.5+B128/(1+0.16)^6.5+B129/(1+0.16)^7.5+B130/(1+0.16)^8.5+B131/(1+0.16)^9.5+B132/(1+0.16)^10.5+B133/(1+0.16)^11.5+B134/(1+0.16)^12.5+B135/(1+0.16)^13.5+B136/(1+0.16)^14.5+B137/(1+0.16)^15.5+B138/(1+0.16)^16.5+B139/(1+0.16)^17.5+B140/(1+0.16)^18.5+B141/(1+0.16)^19.5+B141*(1+0.045)/(0.16-0.045)/(1+0.16)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
@@ -5512,27 +5399,27 @@
           <t>18%</t>
         </is>
       </c>
-      <c r="B80" s="14">
+      <c r="B80" s="13">
         <f>IF(0.18&gt;0.02,(B122/(1+0.18)^0.5+B123/(1+0.18)^1.5+B124/(1+0.18)^2.5+B125/(1+0.18)^3.5+B126/(1+0.18)^4.5+B127/(1+0.18)^5.5+B128/(1+0.18)^6.5+B129/(1+0.18)^7.5+B130/(1+0.18)^8.5+B131/(1+0.18)^9.5+B132/(1+0.18)^10.5+B133/(1+0.18)^11.5+B134/(1+0.18)^12.5+B135/(1+0.18)^13.5+B136/(1+0.18)^14.5+B137/(1+0.18)^15.5+B138/(1+0.18)^16.5+B139/(1+0.18)^17.5+B140/(1+0.18)^18.5+B141/(1+0.18)^19.5+B141*(1+0.02)/(0.18-0.02)/(1+0.18)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="C80" s="14">
+      <c r="C80" s="13">
         <f>IF(0.18&gt;0.025,(B122/(1+0.18)^0.5+B123/(1+0.18)^1.5+B124/(1+0.18)^2.5+B125/(1+0.18)^3.5+B126/(1+0.18)^4.5+B127/(1+0.18)^5.5+B128/(1+0.18)^6.5+B129/(1+0.18)^7.5+B130/(1+0.18)^8.5+B131/(1+0.18)^9.5+B132/(1+0.18)^10.5+B133/(1+0.18)^11.5+B134/(1+0.18)^12.5+B135/(1+0.18)^13.5+B136/(1+0.18)^14.5+B137/(1+0.18)^15.5+B138/(1+0.18)^16.5+B139/(1+0.18)^17.5+B140/(1+0.18)^18.5+B141/(1+0.18)^19.5+B141*(1+0.025)/(0.18-0.025)/(1+0.18)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="D80" s="14">
+      <c r="D80" s="13">
         <f>IF(0.18&gt;0.03,(B122/(1+0.18)^0.5+B123/(1+0.18)^1.5+B124/(1+0.18)^2.5+B125/(1+0.18)^3.5+B126/(1+0.18)^4.5+B127/(1+0.18)^5.5+B128/(1+0.18)^6.5+B129/(1+0.18)^7.5+B130/(1+0.18)^8.5+B131/(1+0.18)^9.5+B132/(1+0.18)^10.5+B133/(1+0.18)^11.5+B134/(1+0.18)^12.5+B135/(1+0.18)^13.5+B136/(1+0.18)^14.5+B137/(1+0.18)^15.5+B138/(1+0.18)^16.5+B139/(1+0.18)^17.5+B140/(1+0.18)^18.5+B141/(1+0.18)^19.5+B141*(1+0.03)/(0.18-0.03)/(1+0.18)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="E80" s="14">
+      <c r="E80" s="13">
         <f>IF(0.18&gt;0.035,(B122/(1+0.18)^0.5+B123/(1+0.18)^1.5+B124/(1+0.18)^2.5+B125/(1+0.18)^3.5+B126/(1+0.18)^4.5+B127/(1+0.18)^5.5+B128/(1+0.18)^6.5+B129/(1+0.18)^7.5+B130/(1+0.18)^8.5+B131/(1+0.18)^9.5+B132/(1+0.18)^10.5+B133/(1+0.18)^11.5+B134/(1+0.18)^12.5+B135/(1+0.18)^13.5+B136/(1+0.18)^14.5+B137/(1+0.18)^15.5+B138/(1+0.18)^16.5+B139/(1+0.18)^17.5+B140/(1+0.18)^18.5+B141/(1+0.18)^19.5+B141*(1+0.035)/(0.18-0.035)/(1+0.18)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="F80" s="14">
+      <c r="F80" s="13">
         <f>IF(0.18&gt;0.04,(B122/(1+0.18)^0.5+B123/(1+0.18)^1.5+B124/(1+0.18)^2.5+B125/(1+0.18)^3.5+B126/(1+0.18)^4.5+B127/(1+0.18)^5.5+B128/(1+0.18)^6.5+B129/(1+0.18)^7.5+B130/(1+0.18)^8.5+B131/(1+0.18)^9.5+B132/(1+0.18)^10.5+B133/(1+0.18)^11.5+B134/(1+0.18)^12.5+B135/(1+0.18)^13.5+B136/(1+0.18)^14.5+B137/(1+0.18)^15.5+B138/(1+0.18)^16.5+B139/(1+0.18)^17.5+B140/(1+0.18)^18.5+B141/(1+0.18)^19.5+B141*(1+0.04)/(0.18-0.04)/(1+0.18)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="G80" s="14">
+      <c r="G80" s="13">
         <f>IF(0.18&gt;0.045,(B122/(1+0.18)^0.5+B123/(1+0.18)^1.5+B124/(1+0.18)^2.5+B125/(1+0.18)^3.5+B126/(1+0.18)^4.5+B127/(1+0.18)^5.5+B128/(1+0.18)^6.5+B129/(1+0.18)^7.5+B130/(1+0.18)^8.5+B131/(1+0.18)^9.5+B132/(1+0.18)^10.5+B133/(1+0.18)^11.5+B134/(1+0.18)^12.5+B135/(1+0.18)^13.5+B136/(1+0.18)^14.5+B137/(1+0.18)^15.5+B138/(1+0.18)^16.5+B139/(1+0.18)^17.5+B140/(1+0.18)^18.5+B141/(1+0.18)^19.5+B141*(1+0.045)/(0.18-0.045)/(1+0.18)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
@@ -5543,27 +5430,27 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="B81" s="14">
+      <c r="B81" s="13">
         <f>IF(0.2&gt;0.02,(B122/(1+0.2)^0.5+B123/(1+0.2)^1.5+B124/(1+0.2)^2.5+B125/(1+0.2)^3.5+B126/(1+0.2)^4.5+B127/(1+0.2)^5.5+B128/(1+0.2)^6.5+B129/(1+0.2)^7.5+B130/(1+0.2)^8.5+B131/(1+0.2)^9.5+B132/(1+0.2)^10.5+B133/(1+0.2)^11.5+B134/(1+0.2)^12.5+B135/(1+0.2)^13.5+B136/(1+0.2)^14.5+B137/(1+0.2)^15.5+B138/(1+0.2)^16.5+B139/(1+0.2)^17.5+B140/(1+0.2)^18.5+B141/(1+0.2)^19.5+B141*(1+0.02)/(0.2-0.02)/(1+0.2)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="C81" s="14">
+      <c r="C81" s="13">
         <f>IF(0.2&gt;0.025,(B122/(1+0.2)^0.5+B123/(1+0.2)^1.5+B124/(1+0.2)^2.5+B125/(1+0.2)^3.5+B126/(1+0.2)^4.5+B127/(1+0.2)^5.5+B128/(1+0.2)^6.5+B129/(1+0.2)^7.5+B130/(1+0.2)^8.5+B131/(1+0.2)^9.5+B132/(1+0.2)^10.5+B133/(1+0.2)^11.5+B134/(1+0.2)^12.5+B135/(1+0.2)^13.5+B136/(1+0.2)^14.5+B137/(1+0.2)^15.5+B138/(1+0.2)^16.5+B139/(1+0.2)^17.5+B140/(1+0.2)^18.5+B141/(1+0.2)^19.5+B141*(1+0.025)/(0.2-0.025)/(1+0.2)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="D81" s="14">
+      <c r="D81" s="13">
         <f>IF(0.2&gt;0.03,(B122/(1+0.2)^0.5+B123/(1+0.2)^1.5+B124/(1+0.2)^2.5+B125/(1+0.2)^3.5+B126/(1+0.2)^4.5+B127/(1+0.2)^5.5+B128/(1+0.2)^6.5+B129/(1+0.2)^7.5+B130/(1+0.2)^8.5+B131/(1+0.2)^9.5+B132/(1+0.2)^10.5+B133/(1+0.2)^11.5+B134/(1+0.2)^12.5+B135/(1+0.2)^13.5+B136/(1+0.2)^14.5+B137/(1+0.2)^15.5+B138/(1+0.2)^16.5+B139/(1+0.2)^17.5+B140/(1+0.2)^18.5+B141/(1+0.2)^19.5+B141*(1+0.03)/(0.2-0.03)/(1+0.2)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="E81" s="14">
+      <c r="E81" s="13">
         <f>IF(0.2&gt;0.035,(B122/(1+0.2)^0.5+B123/(1+0.2)^1.5+B124/(1+0.2)^2.5+B125/(1+0.2)^3.5+B126/(1+0.2)^4.5+B127/(1+0.2)^5.5+B128/(1+0.2)^6.5+B129/(1+0.2)^7.5+B130/(1+0.2)^8.5+B131/(1+0.2)^9.5+B132/(1+0.2)^10.5+B133/(1+0.2)^11.5+B134/(1+0.2)^12.5+B135/(1+0.2)^13.5+B136/(1+0.2)^14.5+B137/(1+0.2)^15.5+B138/(1+0.2)^16.5+B139/(1+0.2)^17.5+B140/(1+0.2)^18.5+B141/(1+0.2)^19.5+B141*(1+0.035)/(0.2-0.035)/(1+0.2)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="F81" s="14">
+      <c r="F81" s="13">
         <f>IF(0.2&gt;0.04,(B122/(1+0.2)^0.5+B123/(1+0.2)^1.5+B124/(1+0.2)^2.5+B125/(1+0.2)^3.5+B126/(1+0.2)^4.5+B127/(1+0.2)^5.5+B128/(1+0.2)^6.5+B129/(1+0.2)^7.5+B130/(1+0.2)^8.5+B131/(1+0.2)^9.5+B132/(1+0.2)^10.5+B133/(1+0.2)^11.5+B134/(1+0.2)^12.5+B135/(1+0.2)^13.5+B136/(1+0.2)^14.5+B137/(1+0.2)^15.5+B138/(1+0.2)^16.5+B139/(1+0.2)^17.5+B140/(1+0.2)^18.5+B141/(1+0.2)^19.5+B141*(1+0.04)/(0.2-0.04)/(1+0.2)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
-      <c r="G81" s="14">
+      <c r="G81" s="13">
         <f>IF(0.2&gt;0.045,(B122/(1+0.2)^0.5+B123/(1+0.2)^1.5+B124/(1+0.2)^2.5+B125/(1+0.2)^3.5+B126/(1+0.2)^4.5+B127/(1+0.2)^5.5+B128/(1+0.2)^6.5+B129/(1+0.2)^7.5+B130/(1+0.2)^8.5+B131/(1+0.2)^9.5+B132/(1+0.2)^10.5+B133/(1+0.2)^11.5+B134/(1+0.2)^12.5+B135/(1+0.2)^13.5+B136/(1+0.2)^14.5+B137/(1+0.2)^15.5+B138/(1+0.2)^16.5+B139/(1+0.2)^17.5+B140/(1+0.2)^18.5+B141/(1+0.2)^19.5+B141*(1+0.045)/(0.2-0.045)/(1+0.2)^20-MAX(0,Assumptions!C32-Assumptions!C27)+MAX(0,Assumptions!C27-Assumptions!C32))*1000/Assumptions!C34,"-")</f>
         <v/>
       </c>
@@ -6756,9 +6643,6 @@
         <v/>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr"/>
-    </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
@@ -6822,15 +6706,15 @@
           <t>Implied Share Price ($)</t>
         </is>
       </c>
-      <c r="B167" s="14">
+      <c r="B167" s="13">
         <f>IF(Assumptions!C34&gt;0,(B166*1000)/Assumptions!C34,0)</f>
         <v/>
       </c>
-      <c r="C167" s="14">
+      <c r="C167" s="13">
         <f>IF(Assumptions!C34&gt;0,(C166*1000)/Assumptions!C34,0)</f>
         <v/>
       </c>
-      <c r="D167" s="14">
+      <c r="D167" s="13">
         <f>IF(Assumptions!C34&gt;0,(D166*1000)/Assumptions!C34,0)</f>
         <v/>
       </c>
